--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-06-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£11.04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£12.68</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£16.26</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£16.54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£22.88</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£23.21</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£26.46</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£28.96</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£28.26</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£34.66</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£42.27</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£43.26</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£43.05</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£720.42</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£904.42</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£29.43</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£36.29</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£39.41</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£43.97</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£44.65</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£48.23</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£44.24</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£1173.28</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£1280.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>£1213.28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-06-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£11.04</t>
+          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /25mm-celotex-tb4025-pir-insulation-board-2400x1200mm-14-p.asp (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x0000027E43251D10&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£12.68</t>
+          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /30mm-celotex-tb4030-pir-insulation-board-2400x1200mm-185-p.asp (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x0000027E45051AD0&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/120mm-celotex/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£42.78</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/130mm-celotex/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/140mm-celotex/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/150mm-celotex/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£750.0</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/165mm-celotex/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>£960.0</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/200mm-celotex/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£31.90</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-375mm-plasterboard-pl4025/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/celotex-62-5mm-insulated-plasterboard-pl4050/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£52.00</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-72-5mm-insulated-plasterboard-pl4060/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£45.50</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4050-50mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4075-75mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>£992.06</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4085-85mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4100-100mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
